--- a/testData/input_UserRights.xlsx
+++ b/testData/input_UserRights.xlsx
@@ -1,98 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UserRights" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="UserRights" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">UserName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScreenName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RightTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaydeep Kar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OneTime Charges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apply_Onetime_Charge</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
       <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
       <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
       <name val="Cambria"/>
+      <charset val="1"/>
       <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <charset val="1"/>
-    </font>
-    <font>
+      <family val="1"/>
       <sz val="10"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -111,14 +82,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -134,56 +105,53 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -424,53 +392,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35"/>
+    <col width="22" customWidth="1" style="5" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="2"/>
+    <col width="35" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+    <row r="1" ht="27.75" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>UserName</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>ScreenName</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>RightTitle</t>
+        </is>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
+    <row r="2" ht="21.75" customHeight="1" s="6">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Jaydeep Kar</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>OneTime Charges</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Apply_Onetime_Charge</t>
+        </is>
       </c>
     </row>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" ht="15" customHeight="1" s="6">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Jaydeep Kar</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Account Statement</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>View_Account_Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="6">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nidhi Chaturvedi</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Program Change</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>View_Account_Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048571" ht="12.75" customHeight="1" s="6"/>
+    <row r="1048572" ht="12.75" customHeight="1" s="6"/>
+    <row r="1048573" ht="12.75" customHeight="1" s="6"/>
+    <row r="1048574" ht="12.75" customHeight="1" s="6"/>
+    <row r="1048575" ht="12.75" customHeight="1" s="6"/>
+    <row r="1048576" ht="12.75" customHeight="1" s="6"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/testData/input_UserRights.xlsx
+++ b/testData/input_UserRights.xlsx
@@ -397,7 +397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -470,6 +470,23 @@
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>View_Account_Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Varsha Jha</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Corporate Account Statement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tieup_SPOC_Access</t>
         </is>
       </c>
     </row>

--- a/testData/input_UserRights.xlsx
+++ b/testData/input_UserRights.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UserRights" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserRights" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -397,7 +397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -474,19 +474,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Varsha Jha</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Corporate Account Statement</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Tieup_SPOC_Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nidhi Chaturvedi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Raise_Support_Request</t>
         </is>
       </c>
     </row>
